--- a/data/gold/results/scenarios/zorg_en_welzijn/table_s5_dk.xlsx
+++ b/data/gold/results/scenarios/zorg_en_welzijn/table_s5_dk.xlsx
@@ -388,13 +388,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>5324.893269721346</v>
+        <v>5282.353787088248</v>
       </c>
       <c r="C2">
-        <v>64720.67119886602</v>
+        <v>77477.50333386465</v>
       </c>
       <c r="D2">
-        <v>8.227500072364275</v>
+        <v>6.817919473121928</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -402,13 +402,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>6047.036127486736</v>
+        <v>4813.127714787854</v>
       </c>
       <c r="C3">
-        <v>81896.03408341862</v>
+        <v>53939.28050941755</v>
       </c>
       <c r="D3">
-        <v>7.383796047226507</v>
+        <v>8.92323306749986</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -416,13 +416,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>46.95906428336476</v>
+        <v>106.1413905251322</v>
       </c>
       <c r="C4">
-        <v>883.0636615745001</v>
+        <v>1276.414575312263</v>
       </c>
       <c r="D4">
-        <v>5.317743932485782</v>
+        <v>8.315589039647696</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -430,13 +430,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>4234.47235581968</v>
+        <v>5581.413491720555</v>
       </c>
       <c r="C5">
-        <v>86351.7602835304</v>
+        <v>99466.18032506436</v>
       </c>
       <c r="D5">
-        <v>4.90374758072802</v>
+        <v>5.61136807855695</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -444,13 +444,13 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1604.461895659503</v>
+        <v>288.6032743741226</v>
       </c>
       <c r="C6">
-        <v>23660.11065987919</v>
+        <v>10587.34124489906</v>
       </c>
       <c r="D6">
-        <v>6.781294976697693</v>
+        <v>2.725927763149889</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/scenarios/zorg_en_welzijn/table_s5_dk.xlsx
+++ b/data/gold/results/scenarios/zorg_en_welzijn/table_s5_dk.xlsx
@@ -402,13 +402,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>4813.127714787854</v>
+        <v>4811.230914787854</v>
       </c>
       <c r="C3">
         <v>53939.28050941755</v>
       </c>
       <c r="D3">
-        <v>8.92323306749986</v>
+        <v>8.919716520779017</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -416,13 +416,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>106.1413905251322</v>
+        <v>106.1278905251322</v>
       </c>
       <c r="C4">
         <v>1276.414575312263</v>
       </c>
       <c r="D4">
-        <v>8.315589039647696</v>
+        <v>8.314531389550218</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -430,13 +430,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>5581.413491720555</v>
+        <v>5581.290291720555</v>
       </c>
       <c r="C5">
         <v>99466.18032506436</v>
       </c>
       <c r="D5">
-        <v>5.61136807855695</v>
+        <v>5.611244217361518</v>
       </c>
     </row>
     <row r="6" spans="1:4">
